--- a/inventory_full.xlsx
+++ b/inventory_full.xlsx
@@ -23230,7 +23230,7 @@
         <v>113</v>
       </c>
       <c r="J413">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K413" t="s">
         <v>34</v>
@@ -23239,7 +23239,7 @@
         <v>243.21</v>
       </c>
       <c r="N413">
-        <v>10701.24</v>
+        <v>0</v>
       </c>
       <c r="O413" t="b">
         <v>0</v>
@@ -28443,10 +28443,10 @@
         <v>229</v>
       </c>
       <c r="AD534" t="s">
-        <v>233</v>
+        <v>38</v>
       </c>
       <c r="AE534" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
     </row>
     <row r="535" spans="1:31">
@@ -28487,10 +28487,10 @@
         <v>237</v>
       </c>
       <c r="AD535" t="s">
-        <v>241</v>
+        <v>38</v>
       </c>
       <c r="AE535" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
     </row>
     <row r="536" spans="1:31">
@@ -28569,10 +28569,10 @@
         <v>254</v>
       </c>
       <c r="AD537" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="AE537" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
     </row>
     <row r="538" spans="1:31">
@@ -28651,10 +28651,10 @@
         <v>263</v>
       </c>
       <c r="AD539" t="s">
-        <v>267</v>
+        <v>38</v>
       </c>
       <c r="AE539" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
     </row>
     <row r="540" spans="1:31">
@@ -28695,10 +28695,10 @@
         <v>279</v>
       </c>
       <c r="AD540" t="s">
-        <v>283</v>
+        <v>38</v>
       </c>
       <c r="AE540" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
     </row>
     <row r="541" spans="1:31">

--- a/inventory_full.xlsx
+++ b/inventory_full.xlsx
@@ -712,7 +712,7 @@
     <t>PER-A-R02</t>
   </si>
   <si>
-    <t>PER-A-R02-01, PER-A-R02-02, PER-A-R02-03</t>
+    <t>PER-A-R02-02, PER-A-R02-03</t>
   </si>
   <si>
     <t>IG-FIBREW-3145</t>
